--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F99EB85-064B-4CBB-B2E0-9C1B90B229EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BCD89B-8C48-4CB9-931A-F032A82FD7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,12 +27,25 @@
     <sheet name="DECIMO" sheetId="12" r:id="rId12"/>
     <sheet name="EXTRA" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="159">
   <si>
     <t>CODIGO</t>
   </si>
@@ -488,19 +501,46 @@
   </si>
   <si>
     <t>DISCIPLINAS EXTRAS - MATRIZ 2020</t>
+  </si>
+  <si>
+    <t>DESENHO TÉCNICO - A (16)</t>
+  </si>
+  <si>
+    <t>INTRODUÇÃO À ENGENHARIA DE ENERGIA (10)</t>
+  </si>
+  <si>
+    <t>GEOMETRIA ANALÍTICA (1)</t>
+  </si>
+  <si>
+    <t>SOCIEDADE E AMBIENTE (32)</t>
+  </si>
+  <si>
+    <t>QUÍMICA GERAL (35)</t>
+  </si>
+  <si>
+    <t>INTRODUÇÃO À COMPUTAÇÃO (10)</t>
+  </si>
+  <si>
+    <t>DESENHO TÉCNICO - B (27)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -520,14 +560,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{AA75590D-80C6-4BB6-9C97-3197281DD4A5}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -3533,7 +3575,10 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3610,7 +3655,7 @@
         <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="F4" t="s">
         <v>121</v>
@@ -3630,7 +3675,7 @@
         <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="F5" t="s">
         <v>121</v>
@@ -3650,7 +3695,7 @@
         <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="F6" t="s">
         <v>121</v>
@@ -3724,16 +3769,16 @@
         <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3741,19 +3786,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3761,19 +3806,19 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3781,19 +3826,19 @@
         <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3801,7 +3846,7 @@
         <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="C14" t="s">
         <v>121</v>
@@ -3810,10 +3855,10 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3837,9 +3882,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D11 E14 F11" xr:uid="{77FDC6AA-4048-4650-9661-0FAA4EA80059}"/>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F3 A15:F15 A12:A14 C14:D14 A10:C11 A7:F9 A4:D6 F4:F6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9BCD89B-8C48-4CB9-931A-F032A82FD7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124E7F9C-0A4D-427F-9D7F-B5B9333AD5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="152">
   <si>
     <t>CODIGO</t>
   </si>
@@ -501,27 +501,6 @@
   </si>
   <si>
     <t>DISCIPLINAS EXTRAS - MATRIZ 2020</t>
-  </si>
-  <si>
-    <t>DESENHO TÉCNICO - A (16)</t>
-  </si>
-  <si>
-    <t>INTRODUÇÃO À ENGENHARIA DE ENERGIA (10)</t>
-  </si>
-  <si>
-    <t>GEOMETRIA ANALÍTICA (1)</t>
-  </si>
-  <si>
-    <t>SOCIEDADE E AMBIENTE (32)</t>
-  </si>
-  <si>
-    <t>QUÍMICA GERAL (35)</t>
-  </si>
-  <si>
-    <t>INTRODUÇÃO À COMPUTAÇÃO (10)</t>
-  </si>
-  <si>
-    <t>DESENHO TÉCNICO - B (27)</t>
   </si>
 </sst>
 </file>
@@ -907,9 +886,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -926,7 +905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -934,7 +913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -942,7 +921,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -950,7 +929,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -958,7 +937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -966,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -974,7 +953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -982,7 +961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -990,7 +969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -998,7 +977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1006,7 +985,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1014,7 +993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1022,7 +1001,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1030,7 +1009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1038,7 +1017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1046,7 +1025,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1054,7 +1033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1062,7 +1041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1070,7 +1049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1078,7 +1057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1086,7 +1065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1094,7 +1073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1102,7 +1081,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1110,7 +1089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1118,7 +1097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1126,7 +1105,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1134,7 +1113,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1142,7 +1121,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1150,7 +1129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1158,7 +1137,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1166,7 +1145,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1174,7 +1153,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1182,7 +1161,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1190,7 +1169,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>35</v>
       </c>
@@ -1198,7 +1177,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>36</v>
       </c>
@@ -1217,9 +1196,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>146</v>
       </c>
@@ -1239,7 +1218,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -1259,7 +1238,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -1279,7 +1258,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -1299,7 +1278,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -1319,7 +1298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -1339,7 +1318,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -1359,7 +1338,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -1379,7 +1358,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -1399,7 +1378,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -1419,7 +1398,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -1439,7 +1418,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -1459,7 +1438,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -1479,7 +1458,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -1499,7 +1478,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -1530,9 +1509,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>147</v>
       </c>
@@ -1552,7 +1531,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -1572,7 +1551,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -1592,7 +1571,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -1612,7 +1591,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -1632,7 +1611,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -1652,7 +1631,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -1672,7 +1651,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -1692,7 +1671,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -1712,7 +1691,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -1732,7 +1711,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -1752,7 +1731,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -1772,7 +1751,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -1792,7 +1771,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -1812,7 +1791,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -1843,9 +1822,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>150</v>
       </c>
@@ -1865,7 +1844,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -1885,7 +1864,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -1905,7 +1884,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -1925,7 +1904,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -1945,7 +1924,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -1965,7 +1944,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -1985,7 +1964,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -2005,7 +1984,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -2025,7 +2004,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -2045,7 +2024,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -2065,7 +2044,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -2085,7 +2064,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -2105,7 +2084,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -2125,7 +2104,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -2156,9 +2135,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>151</v>
       </c>
@@ -2178,7 +2157,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -2198,7 +2177,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -2218,7 +2197,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -2238,7 +2217,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -2258,7 +2237,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -2278,7 +2257,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -2298,7 +2277,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -2318,7 +2297,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -2338,7 +2317,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -2358,7 +2337,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -2378,7 +2357,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -2398,7 +2377,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -2418,7 +2397,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -2438,7 +2417,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -2469,9 +2448,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H64"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2497,7 +2476,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2514,7 +2493,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -2531,7 +2510,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -2548,7 +2527,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -2565,7 +2544,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -2582,7 +2561,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -2599,7 +2578,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -2616,7 +2595,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -2633,7 +2612,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -2650,7 +2629,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -2667,7 +2646,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -2684,7 +2663,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -2701,7 +2680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -2718,7 +2697,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -2735,7 +2714,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -2752,7 +2731,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -2769,7 +2748,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -2786,7 +2765,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -2803,7 +2782,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -2820,7 +2799,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -2837,7 +2816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -2854,7 +2833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -2871,7 +2850,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
@@ -2888,7 +2867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -2905,7 +2884,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -2922,7 +2901,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -2939,7 +2918,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
@@ -2956,7 +2935,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -2973,7 +2952,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -2990,7 +2969,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -3007,7 +2986,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -3024,7 +3003,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -3041,7 +3020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -3058,7 +3037,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -3075,7 +3054,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>79</v>
       </c>
@@ -3092,7 +3071,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>87</v>
       </c>
@@ -3109,7 +3088,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>87</v>
       </c>
@@ -3126,7 +3105,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -3143,7 +3122,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>87</v>
       </c>
@@ -3160,7 +3139,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -3177,7 +3156,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
@@ -3194,7 +3173,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -3211,7 +3190,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
@@ -3228,7 +3207,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -3245,7 +3224,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>95</v>
       </c>
@@ -3262,7 +3241,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -3279,7 +3258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -3296,7 +3275,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>95</v>
       </c>
@@ -3313,7 +3292,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>95</v>
       </c>
@@ -3330,7 +3309,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>95</v>
       </c>
@@ -3347,7 +3326,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -3364,7 +3343,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -3381,7 +3360,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
@@ -3398,7 +3377,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
@@ -3415,7 +3394,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>104</v>
       </c>
@@ -3432,7 +3411,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>104</v>
       </c>
@@ -3449,7 +3428,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
@@ -3466,7 +3445,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -3483,7 +3462,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>111</v>
       </c>
@@ -3500,7 +3479,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>111</v>
       </c>
@@ -3517,7 +3496,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>111</v>
       </c>
@@ -3534,7 +3513,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>117</v>
       </c>
@@ -3548,7 +3527,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>119</v>
       </c>
@@ -3573,7 +3552,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
@@ -3581,7 +3560,7 @@
     <col min="5" max="5" width="25.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>120</v>
       </c>
@@ -3601,7 +3580,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -3621,7 +3600,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -3641,7 +3620,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -3654,14 +3633,11 @@
       <c r="D4" t="s">
         <v>121</v>
       </c>
-      <c r="E4" t="s">
-        <v>158</v>
-      </c>
       <c r="F4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -3674,14 +3650,11 @@
       <c r="D5" t="s">
         <v>121</v>
       </c>
-      <c r="E5" t="s">
-        <v>158</v>
-      </c>
       <c r="F5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -3694,14 +3667,11 @@
       <c r="D6" t="s">
         <v>121</v>
       </c>
-      <c r="E6" t="s">
-        <v>158</v>
-      </c>
       <c r="F6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -3721,7 +3691,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -3741,7 +3711,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -3761,7 +3731,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -3772,16 +3742,10 @@
         <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -3792,76 +3756,31 @@
         <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E12" t="s">
-        <v>155</v>
-      </c>
-      <c r="F12" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
-      <c r="B13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B14" t="s">
-        <v>152</v>
-      </c>
       <c r="C14" t="s">
         <v>121</v>
       </c>
       <c r="D14" t="s">
         <v>121</v>
       </c>
-      <c r="E14" t="s">
-        <v>156</v>
-      </c>
-      <c r="F14" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -3883,7 +3802,7 @@
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D11 E14 F11" xr:uid="{77FDC6AA-4048-4650-9661-0FAA4EA80059}"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F11 E14" xr:uid="{77FDC6AA-4048-4650-9661-0FAA4EA80059}"/>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -3895,9 +3814,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>140</v>
       </c>
@@ -3917,7 +3836,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -3937,7 +3856,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -3957,7 +3876,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -3977,7 +3896,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -3997,7 +3916,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -4017,7 +3936,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -4037,7 +3956,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -4057,7 +3976,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -4077,7 +3996,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -4097,7 +4016,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4117,7 +4036,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -4137,7 +4056,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -4157,7 +4076,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -4177,7 +4096,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -4208,9 +4127,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>141</v>
       </c>
@@ -4230,7 +4149,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -4250,7 +4169,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -4270,7 +4189,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -4290,7 +4209,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -4310,7 +4229,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -4330,7 +4249,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -4350,7 +4269,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -4370,7 +4289,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -4390,7 +4309,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -4410,7 +4329,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4430,7 +4349,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -4450,7 +4369,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -4470,7 +4389,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -4490,7 +4409,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -4521,9 +4440,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>142</v>
       </c>
@@ -4543,7 +4462,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -4563,7 +4482,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -4583,7 +4502,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -4603,7 +4522,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -4623,7 +4542,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -4643,7 +4562,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -4663,7 +4582,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -4683,7 +4602,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -4703,7 +4622,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -4723,7 +4642,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -4743,7 +4662,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -4763,7 +4682,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -4783,7 +4702,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -4803,7 +4722,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -4834,9 +4753,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>143</v>
       </c>
@@ -4856,7 +4775,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -4876,7 +4795,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -4896,7 +4815,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -4916,7 +4835,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -4936,7 +4855,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -4956,7 +4875,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -4976,7 +4895,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -4996,7 +4915,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -5016,7 +4935,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -5036,7 +4955,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -5056,7 +4975,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5076,7 +4995,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -5096,7 +5015,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -5116,7 +5035,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -5147,9 +5066,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>144</v>
       </c>
@@ -5169,7 +5088,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -5189,7 +5108,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -5209,7 +5128,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -5229,7 +5148,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -5249,7 +5168,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -5269,7 +5188,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -5289,7 +5208,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -5309,7 +5228,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -5329,7 +5248,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -5349,7 +5268,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -5369,7 +5288,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5389,7 +5308,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -5409,7 +5328,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -5429,7 +5348,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
@@ -5460,9 +5379,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>145</v>
       </c>
@@ -5482,7 +5401,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -5502,7 +5421,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -5522,7 +5441,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
@@ -5542,7 +5461,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>129</v>
       </c>
@@ -5562,7 +5481,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -5582,7 +5501,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -5602,7 +5521,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -5622,7 +5541,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>121</v>
       </c>
@@ -5642,7 +5561,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>133</v>
       </c>
@@ -5662,7 +5581,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -5682,7 +5601,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
@@ -5702,7 +5621,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
@@ -5722,7 +5641,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
@@ -5742,7 +5661,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124E7F9C-0A4D-427F-9D7F-B5B9333AD5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2B1F0D-6708-43FF-82B5-B28F98B4409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="153">
   <si>
     <t>CODIGO</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>DISCIPLINAS EXTRAS - MATRIZ 2020</t>
+  </si>
+  <si>
+    <t>DESENHO TÉCNICO - A (16)</t>
   </si>
 </sst>
 </file>
@@ -3741,9 +3744,6 @@
       <c r="C10" t="s">
         <v>134</v>
       </c>
-      <c r="D10" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -3755,23 +3755,29 @@
       <c r="C11" t="s">
         <v>134</v>
       </c>
-      <c r="D11" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
+      <c r="B12" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
+      <c r="B13" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
       </c>
       <c r="C14" t="s">
         <v>121</v>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2B1F0D-6708-43FF-82B5-B28F98B4409D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E898D83B-6654-428C-A9D9-7DF11031BCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="159">
   <si>
     <t>CODIGO</t>
   </si>
@@ -504,6 +504,24 @@
   </si>
   <si>
     <t>DESENHO TÉCNICO - A (16)</t>
+  </si>
+  <si>
+    <t>GEOMETRIA ANALÍTICA (1)</t>
+  </si>
+  <si>
+    <t>INTRODUÇÃO À ENGENHARIA DE ENERGIA (10)</t>
+  </si>
+  <si>
+    <t>SOCIEDADE E AMBIENTE (32)</t>
+  </si>
+  <si>
+    <t>QUÍMICA GERAL (35)</t>
+  </si>
+  <si>
+    <t>INTRODUÇÃO À COMPUTAÇÃO (10)</t>
+  </si>
+  <si>
+    <t>DESENHO TÉCNICO - B (27)</t>
   </si>
 </sst>
 </file>
@@ -3636,6 +3654,9 @@
       <c r="D4" t="s">
         <v>121</v>
       </c>
+      <c r="E4" t="s">
+        <v>158</v>
+      </c>
       <c r="F4" t="s">
         <v>121</v>
       </c>
@@ -3653,6 +3674,9 @@
       <c r="D5" t="s">
         <v>121</v>
       </c>
+      <c r="E5" t="s">
+        <v>158</v>
+      </c>
       <c r="F5" t="s">
         <v>121</v>
       </c>
@@ -3670,6 +3694,9 @@
       <c r="D6" t="s">
         <v>121</v>
       </c>
+      <c r="E6" t="s">
+        <v>158</v>
+      </c>
       <c r="F6" t="s">
         <v>121</v>
       </c>
@@ -3744,6 +3771,15 @@
       <c r="C10" t="s">
         <v>134</v>
       </c>
+      <c r="D10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -3755,6 +3791,15 @@
       <c r="C11" t="s">
         <v>134</v>
       </c>
+      <c r="D11" t="s">
+        <v>154</v>
+      </c>
+      <c r="E11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -3763,6 +3808,18 @@
       <c r="B12" t="s">
         <v>152</v>
       </c>
+      <c r="C12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -3771,6 +3828,18 @@
       <c r="B13" t="s">
         <v>152</v>
       </c>
+      <c r="C13" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -3785,6 +3854,12 @@
       <c r="D14" t="s">
         <v>121</v>
       </c>
+      <c r="E14" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -3807,8 +3882,8 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F11 E14" xr:uid="{77FDC6AA-4048-4650-9661-0FAA4EA80059}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D11 E14 F11" xr:uid="{77FDC6AA-4048-4650-9661-0FAA4EA80059}"/>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E898D83B-6654-428C-A9D9-7DF11031BCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2F03A9-9437-4DD1-B8BA-3609300092B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="167">
   <si>
     <t>CODIGO</t>
   </si>
@@ -522,6 +522,30 @@
   </si>
   <si>
     <t>DESENHO TÉCNICO - B (27)</t>
+  </si>
+  <si>
+    <t>HIDROLOGIA (EXT)</t>
+  </si>
+  <si>
+    <t>CÁLCULO III (31)</t>
+  </si>
+  <si>
+    <t>FÍSICA II (26)</t>
+  </si>
+  <si>
+    <t>DESENHO TÉCNICO INDUSTRIAL (7)</t>
+  </si>
+  <si>
+    <t>DESENHO UNIVERSAL (16)</t>
+  </si>
+  <si>
+    <t>AGROMETEOROLOGIA E CLIMATOLOGIA (23)</t>
+  </si>
+  <si>
+    <t>METODOLOGIA DA PESQUISA (10)</t>
+  </si>
+  <si>
+    <t>CIÊNCIAS DO AMBIENTE E MANEJO DE RECURSOS NATURAIS (3)</t>
   </si>
 </sst>
 </file>
@@ -4209,6 +4233,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="30.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4367,7 +4395,7 @@
         <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4387,7 +4415,7 @@
         <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,19 +4423,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,19 +4443,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4435,19 +4463,16 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,65 +4480,47 @@
         <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" t="s">
-        <v>121</v>
-      </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="E14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>139</v>
       </c>
-      <c r="B15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" t="s">
-        <v>121</v>
-      </c>
       <c r="D15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" t="s">
-        <v>121</v>
-      </c>
-      <c r="F15" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C10:C11 B10:B13 E12:E15 F8:F9" xr:uid="{678DE51D-8AC9-488A-B3F9-4D2216B16875}"/>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F7 A10:A15 A8:E9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2F03A9-9437-4DD1-B8BA-3609300092B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D698D-534C-4877-9CEB-FA02D9A59C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -524,15 +524,6 @@
     <t>DESENHO TÉCNICO - B (27)</t>
   </si>
   <si>
-    <t>HIDROLOGIA (EXT)</t>
-  </si>
-  <si>
-    <t>CÁLCULO III (31)</t>
-  </si>
-  <si>
-    <t>FÍSICA II (26)</t>
-  </si>
-  <si>
     <t>DESENHO TÉCNICO INDUSTRIAL (7)</t>
   </si>
   <si>
@@ -546,6 +537,15 @@
   </si>
   <si>
     <t>CIÊNCIAS DO AMBIENTE E MANEJO DE RECURSOS NATURAIS (3)</t>
+  </si>
+  <si>
+    <t>HIDROLOGIA (36)</t>
+  </si>
+  <si>
+    <t>CÁLCULO 3 (31)</t>
+  </si>
+  <si>
+    <t>FÍSICA 2 (26)</t>
   </si>
 </sst>
 </file>
@@ -4234,8 +4234,11 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4395,7 +4398,7 @@
         <v>121</v>
       </c>
       <c r="F8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4415,7 +4418,7 @@
         <v>121</v>
       </c>
       <c r="F9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4423,19 +4426,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" t="s">
         <v>159</v>
       </c>
-      <c r="C10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" t="s">
-        <v>162</v>
-      </c>
       <c r="F10" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4443,19 +4446,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E11" t="s">
         <v>159</v>
       </c>
-      <c r="C11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" t="s">
-        <v>162</v>
-      </c>
       <c r="F11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4463,16 +4466,16 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4480,19 +4483,19 @@
         <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C13" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E13" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4500,10 +4503,10 @@
         <v>138</v>
       </c>
       <c r="D14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E14" t="s">
         <v>165</v>
-      </c>
-      <c r="E14" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,7 +4514,7 @@
         <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0D698D-534C-4877-9CEB-FA02D9A59C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38C9676-59E3-4080-9DC4-99254915B558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="180">
   <si>
     <t>CODIGO</t>
   </si>
@@ -546,6 +546,45 @@
   </si>
   <si>
     <t>FÍSICA 2 (26)</t>
+  </si>
+  <si>
+    <t>CÁLCULO IV (25)</t>
+  </si>
+  <si>
+    <t>ENERGIA DE BIOMASSA E CAPTAÇÃO DE CARBONO (23)</t>
+  </si>
+  <si>
+    <t>MECÂNICA DOS SÓLIDOS I (17)</t>
+  </si>
+  <si>
+    <t>ACE I (1)</t>
+  </si>
+  <si>
+    <t>BIOQUÍMICA (4)</t>
+  </si>
+  <si>
+    <t>FÍSICA III (8)</t>
+  </si>
+  <si>
+    <t>ACE III (11)</t>
+  </si>
+  <si>
+    <t>TRANSFERÊNCIA DE CALOR (7)</t>
+  </si>
+  <si>
+    <t>MICROBIOLOGIA GERAL (12)</t>
+  </si>
+  <si>
+    <t>MECÂNICA DOS SÓLIDOS III (29)</t>
+  </si>
+  <si>
+    <t>CIÊNCIAS DOS MATERIAIS (17)</t>
+  </si>
+  <si>
+    <t>QUÍMICA ANALÍTICA (13)</t>
+  </si>
+  <si>
+    <t>ANÁLISE DE CIRCUITOS ELÉTRICOS (15)</t>
   </si>
 </sst>
 </file>
@@ -4532,6 +4571,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="14.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4658,19 +4700,10 @@
         <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4678,19 +4711,10 @@
         <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4718,19 +4742,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4738,19 +4762,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4758,39 +4782,30 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
-      <c r="B13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" t="s">
-        <v>121</v>
-      </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4834,9 +4849,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F7:F8" xr:uid="{5EBF3668-5F9A-4909-8FE4-B135A740F455}"/>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F6 A9:F9 A7:A8 A14:F15 A10:A13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5204,7 +5222,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
@@ -5224,7 +5242,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -5244,7 +5262,7 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
@@ -5344,19 +5362,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5364,19 +5382,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5384,59 +5402,44 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
-      <c r="B13" t="s">
-        <v>121</v>
-      </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B14" t="s">
-        <v>121</v>
-      </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5460,9 +5463,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B3:B5 B10:B11" xr:uid="{9C087D3E-C77C-4FA1-B64D-C267CDBE5ED7}"/>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F2 A6:F9 A3:A5 C3:F5 A15:F15 A10:A14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38C9676-59E3-4080-9DC4-99254915B558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A48F7DB-A9CC-40B3-B8C0-B14D63F0AF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -554,9 +554,6 @@
     <t>ENERGIA DE BIOMASSA E CAPTAÇÃO DE CARBONO (23)</t>
   </si>
   <si>
-    <t>MECÂNICA DOS SÓLIDOS I (17)</t>
-  </si>
-  <si>
     <t>ACE I (1)</t>
   </si>
   <si>
@@ -575,9 +572,6 @@
     <t>MICROBIOLOGIA GERAL (12)</t>
   </si>
   <si>
-    <t>MECÂNICA DOS SÓLIDOS III (29)</t>
-  </si>
-  <si>
     <t>CIÊNCIAS DOS MATERIAIS (17)</t>
   </si>
   <si>
@@ -585,6 +579,12 @@
   </si>
   <si>
     <t>ANÁLISE DE CIRCUITOS ELÉTRICOS (15)</t>
+  </si>
+  <si>
+    <t>MECÂNICA DOS SÓLIDOS 3 (29)</t>
+  </si>
+  <si>
+    <t>MECÂNICA DOS SÓLIDOS 1 (17)</t>
   </si>
 </sst>
 </file>
@@ -4745,16 +4745,16 @@
         <v>168</v>
       </c>
       <c r="C10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" t="s">
         <v>169</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>170</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>171</v>
-      </c>
-      <c r="F10" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4765,16 +4765,16 @@
         <v>168</v>
       </c>
       <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" t="s">
         <v>169</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>170</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>171</v>
-      </c>
-      <c r="F11" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4785,13 +4785,13 @@
         <v>168</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E12" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4799,13 +4799,13 @@
         <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5222,7 +5222,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
@@ -5242,7 +5242,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -5262,7 +5262,7 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
@@ -5362,19 +5362,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" t="s">
         <v>174</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" t="s">
         <v>175</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>176</v>
-      </c>
-      <c r="E10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F10" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5382,19 +5382,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" t="s">
         <v>174</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" t="s">
         <v>175</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>176</v>
-      </c>
-      <c r="E11" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5402,19 +5402,19 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
         <v>174</v>
       </c>
-      <c r="C12" t="s">
-        <v>179</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>176</v>
-      </c>
-      <c r="E12" t="s">
-        <v>175</v>
-      </c>
-      <c r="F12" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5422,13 +5422,13 @@
         <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5436,10 +5436,10 @@
         <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A48F7DB-A9CC-40B3-B8C0-B14D63F0AF05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77C706C-929F-4DBE-AD0A-0D46482BAAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="184">
   <si>
     <t>CODIGO</t>
   </si>
@@ -585,6 +585,18 @@
   </si>
   <si>
     <t>MECÂNICA DOS SÓLIDOS 1 (17)</t>
+  </si>
+  <si>
+    <t>CURSO</t>
+  </si>
+  <si>
+    <t>ENGENHARIA DE ENERGIA</t>
+  </si>
+  <si>
+    <t>DECIMO</t>
+  </si>
+  <si>
+    <t>Tópicos Especiais em Eficiência Energética em Edifícios</t>
   </si>
 </sst>
 </file>
@@ -2531,10 +2543,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="45.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2545,1090 +2565,1308 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" t="s">
         <v>41</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
       <c r="B2" t="s">
         <v>47</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>72</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>54</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>36</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>46</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>72</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>46</v>
       </c>
       <c r="B6" t="s">
         <v>52</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>54</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>46</v>
       </c>
       <c r="B7" t="s">
         <v>53</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>46</v>
       </c>
       <c r="B8" t="s">
         <v>54</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>54</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>46</v>
       </c>
       <c r="B9" t="s">
         <v>55</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9">
         <v>4</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>72</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10">
         <v>4</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
       <c r="B11" t="s">
         <v>58</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11">
         <v>3</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>54</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>56</v>
       </c>
       <c r="B12" t="s">
         <v>59</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12">
         <v>4</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>72</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>56</v>
       </c>
       <c r="B13" t="s">
         <v>60</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13">
         <v>4</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>72</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>61</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E14">
         <v>4</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>72</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>62</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E15">
         <v>4</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>72</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>63</v>
       </c>
       <c r="B16" t="s">
         <v>64</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="s">
+        <v>181</v>
+      </c>
+      <c r="E16">
         <v>2</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>36</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
       <c r="B17" t="s">
         <v>65</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17">
         <v>4</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>72</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
       <c r="B18" t="s">
         <v>66</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18">
         <v>4</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>72</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
       <c r="B19" t="s">
         <v>67</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E19">
         <v>2</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>36</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
       <c r="B20" t="s">
         <v>68</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20">
         <v>2</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>36</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
       <c r="B21" t="s">
         <v>69</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21">
         <v>2</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>36</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>63</v>
       </c>
       <c r="B22" t="s">
         <v>70</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22">
         <v>4</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>72</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>63</v>
       </c>
       <c r="B23" t="s">
         <v>71</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="s">
+        <v>181</v>
+      </c>
+      <c r="E23">
         <v>4</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>72</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
       <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24">
         <v>4</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>72</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
       <c r="B25" t="s">
         <v>74</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="s">
+        <v>181</v>
+      </c>
+      <c r="E25">
         <v>4</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>72</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>72</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26">
         <v>3</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>72</v>
       </c>
       <c r="B27" t="s">
         <v>76</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E27">
         <v>4</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>72</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>72</v>
       </c>
       <c r="B28" t="s">
         <v>77</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28">
         <v>4</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>72</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>72</v>
       </c>
       <c r="B29" t="s">
         <v>78</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="s">
+        <v>181</v>
+      </c>
+      <c r="E29">
         <v>2</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>36</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>79</v>
       </c>
       <c r="B30" t="s">
         <v>80</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30">
         <v>4</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>72</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>79</v>
       </c>
       <c r="B31" t="s">
         <v>81</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31">
         <v>3</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>54</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>79</v>
       </c>
       <c r="B32" t="s">
         <v>82</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32">
         <v>3</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>54</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
       <c r="B33" t="s">
         <v>83</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33">
         <v>4</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>72</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
       <c r="B34" t="s">
         <v>84</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34">
         <v>2</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>36</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
       <c r="B35" t="s">
         <v>85</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35">
         <v>4</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>72</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>79</v>
       </c>
       <c r="B36" t="s">
         <v>86</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36">
         <v>2</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>36</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>87</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="s">
+        <v>181</v>
+      </c>
+      <c r="E37">
         <v>3</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>54</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>87</v>
       </c>
       <c r="B38" t="s">
         <v>89</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38">
         <v>4</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>72</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
       <c r="B39" t="s">
         <v>90</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="s">
+        <v>181</v>
+      </c>
+      <c r="E39">
         <v>3</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>54</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>87</v>
       </c>
       <c r="B40" t="s">
         <v>91</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="s">
+        <v>181</v>
+      </c>
+      <c r="E40">
         <v>4</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>72</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>87</v>
       </c>
       <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41">
         <v>3</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>54</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>87</v>
       </c>
       <c r="B42" t="s">
         <v>93</v>
       </c>
-      <c r="D42">
+      <c r="D42" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42">
         <v>3</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>54</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
       <c r="B43" t="s">
         <v>94</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="s">
+        <v>181</v>
+      </c>
+      <c r="E43">
         <v>2</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>36</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
       <c r="B44" t="s">
         <v>96</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="s">
+        <v>181</v>
+      </c>
+      <c r="E44">
         <v>4</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>72</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>95</v>
       </c>
       <c r="B45" t="s">
         <v>97</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45">
         <v>2</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>36</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>95</v>
       </c>
       <c r="B46" t="s">
         <v>98</v>
       </c>
-      <c r="D46">
+      <c r="D46" t="s">
+        <v>181</v>
+      </c>
+      <c r="E46">
         <v>3</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>54</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
       <c r="B47" t="s">
         <v>99</v>
       </c>
-      <c r="D47">
+      <c r="D47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E47">
         <v>3</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>54</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>95</v>
       </c>
       <c r="B48" t="s">
         <v>100</v>
       </c>
-      <c r="D48">
+      <c r="D48" t="s">
+        <v>181</v>
+      </c>
+      <c r="E48">
         <v>3</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>54</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>95</v>
       </c>
       <c r="B49" t="s">
         <v>101</v>
       </c>
-      <c r="D49">
+      <c r="D49" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49">
         <v>4</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>72</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>95</v>
       </c>
       <c r="B50" t="s">
         <v>102</v>
       </c>
-      <c r="D50">
+      <c r="D50" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50">
         <v>4</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>72</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>95</v>
       </c>
       <c r="B51" t="s">
         <v>103</v>
       </c>
-      <c r="D51">
+      <c r="D51" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51">
         <v>2</v>
       </c>
-      <c r="E51">
+      <c r="F51">
         <v>36</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>104</v>
       </c>
       <c r="B52" t="s">
         <v>105</v>
       </c>
-      <c r="D52">
+      <c r="D52" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52">
         <v>4</v>
       </c>
-      <c r="E52">
+      <c r="F52">
         <v>72</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>104</v>
       </c>
       <c r="B53" t="s">
         <v>106</v>
       </c>
-      <c r="D53">
+      <c r="D53" t="s">
+        <v>181</v>
+      </c>
+      <c r="E53">
         <v>4</v>
       </c>
-      <c r="E53">
+      <c r="F53">
         <v>72</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>104</v>
       </c>
       <c r="B54" t="s">
         <v>107</v>
       </c>
-      <c r="D54">
+      <c r="D54" t="s">
+        <v>181</v>
+      </c>
+      <c r="E54">
         <v>3</v>
       </c>
-      <c r="E54">
+      <c r="F54">
         <v>54</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>104</v>
       </c>
       <c r="B55" t="s">
         <v>108</v>
       </c>
-      <c r="D55">
+      <c r="D55" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55">
         <v>3</v>
       </c>
-      <c r="E55">
+      <c r="F55">
         <v>54</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>104</v>
       </c>
       <c r="B56" t="s">
         <v>109</v>
       </c>
-      <c r="D56">
+      <c r="D56" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56">
         <v>2</v>
       </c>
-      <c r="E56">
+      <c r="F56">
         <v>36</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>104</v>
       </c>
       <c r="B57" t="s">
         <v>110</v>
       </c>
-      <c r="D57">
+      <c r="D57" t="s">
+        <v>181</v>
+      </c>
+      <c r="E57">
         <v>2</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>36</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>111</v>
       </c>
       <c r="B58" t="s">
         <v>112</v>
       </c>
-      <c r="D58">
+      <c r="D58" t="s">
+        <v>181</v>
+      </c>
+      <c r="E58">
         <v>4</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>72</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>111</v>
       </c>
       <c r="B59" t="s">
         <v>113</v>
       </c>
-      <c r="D59">
+      <c r="D59" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59">
         <v>3</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>54</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>111</v>
       </c>
       <c r="B60" t="s">
         <v>114</v>
       </c>
-      <c r="D60">
+      <c r="D60" t="s">
+        <v>181</v>
+      </c>
+      <c r="E60">
         <v>3</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>54</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>111</v>
       </c>
       <c r="B61" t="s">
         <v>115</v>
       </c>
-      <c r="D61">
+      <c r="D61" t="s">
+        <v>181</v>
+      </c>
+      <c r="E61">
         <v>3</v>
       </c>
-      <c r="E61">
+      <c r="F61">
         <v>54</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>111</v>
       </c>
       <c r="B62" t="s">
         <v>116</v>
       </c>
-      <c r="D62">
+      <c r="D62" t="s">
+        <v>181</v>
+      </c>
+      <c r="E62">
         <v>2</v>
       </c>
-      <c r="E62">
+      <c r="F62">
         <v>36</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
       <c r="B63" t="s">
         <v>117</v>
       </c>
-      <c r="D63">
+      <c r="D63" t="s">
+        <v>181</v>
+      </c>
+      <c r="E63">
         <v>3</v>
       </c>
-      <c r="E63">
+      <c r="F63">
         <v>54</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>182</v>
+      </c>
       <c r="B64" t="s">
         <v>119</v>
       </c>
-      <c r="D64">
+      <c r="D64" t="s">
+        <v>181</v>
+      </c>
+      <c r="E64">
         <v>3</v>
       </c>
-      <c r="E64">
+      <c r="F64">
         <v>54</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="D65" t="s">
+        <v>181</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>36</v>
+      </c>
+      <c r="G65" t="s">
         <v>118</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H64" numberStoredAsText="1"/>
+    <ignoredError sqref="E1:I64 A1:C62 B64:C64 B63:C63" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5176,6 +5414,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="27.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77C706C-929F-4DBE-AD0A-0D46482BAAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8524DA78-77BE-4BD7-B24D-EFEC868B0722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="191">
   <si>
     <t>CODIGO</t>
   </si>
@@ -563,9 +563,6 @@
     <t>FÍSICA III (8)</t>
   </si>
   <si>
-    <t>ACE III (11)</t>
-  </si>
-  <si>
     <t>TRANSFERÊNCIA DE CALOR (7)</t>
   </si>
   <si>
@@ -597,6 +594,30 @@
   </si>
   <si>
     <t>Tópicos Especiais em Eficiência Energética em Edifícios</t>
+  </si>
+  <si>
+    <t>ACE 3 (11)</t>
+  </si>
+  <si>
+    <t>CONVERSÃO ELETROMECÂNICA (2)</t>
+  </si>
+  <si>
+    <t>BIODIESEL (5)</t>
+  </si>
+  <si>
+    <t>MÁQUINAS DE FLUXO, GERAÇÃO E PROPULSÃO (5)</t>
+  </si>
+  <si>
+    <t>ECONOMIA PARA ENGENHARIA (30)</t>
+  </si>
+  <si>
+    <t>BIOPROCESSOS (19)</t>
+  </si>
+  <si>
+    <t>ACE V (35)</t>
+  </si>
+  <si>
+    <t> ELABORAÇÃO E ANÁLISE DE PROJETOS (21)</t>
   </si>
 </sst>
 </file>
@@ -1293,6 +1314,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1479,19 +1504,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1499,79 +1524,58 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="F11" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>136</v>
       </c>
-      <c r="B12" t="s">
-        <v>121</v>
-      </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="F12" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>137</v>
       </c>
-      <c r="B13" t="s">
-        <v>121</v>
-      </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F13" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>138</v>
       </c>
-      <c r="B14" t="s">
-        <v>121</v>
-      </c>
       <c r="C14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1595,9 +1599,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B14 F13:F14" xr:uid="{C374F044-CB71-49C0-8DA1-4C2C733EA191}"/>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F9 A15:F15 A10:A14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2232,6 +2239,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="33.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2458,7 +2468,7 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
         <v>121</v>
@@ -2478,7 +2488,7 @@
         <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
         <v>121</v>
@@ -2498,7 +2508,7 @@
         <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
         <v>121</v>
@@ -2536,7 +2546,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F15" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F11 A15:F15 A12:A14 C12:F14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2565,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E1" t="s">
         <v>41</v>
@@ -2591,7 +2601,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -2611,7 +2621,7 @@
         <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2631,7 +2641,7 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2651,7 +2661,7 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2671,7 +2681,7 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -2691,7 +2701,7 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -2711,7 +2721,7 @@
         <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -2731,7 +2741,7 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -2751,7 +2761,7 @@
         <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -2771,7 +2781,7 @@
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -2791,7 +2801,7 @@
         <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -2811,7 +2821,7 @@
         <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -2831,7 +2841,7 @@
         <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -2851,7 +2861,7 @@
         <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -2871,7 +2881,7 @@
         <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -2891,7 +2901,7 @@
         <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -2911,7 +2921,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -2931,7 +2941,7 @@
         <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2951,7 +2961,7 @@
         <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2971,7 +2981,7 @@
         <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -2991,7 +3001,7 @@
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -3011,7 +3021,7 @@
         <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -3031,7 +3041,7 @@
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -3051,7 +3061,7 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -3071,7 +3081,7 @@
         <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -3091,7 +3101,7 @@
         <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -3111,7 +3121,7 @@
         <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -3131,7 +3141,7 @@
         <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -3151,7 +3161,7 @@
         <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -3171,7 +3181,7 @@
         <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -3191,7 +3201,7 @@
         <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -3211,7 +3221,7 @@
         <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -3231,7 +3241,7 @@
         <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -3251,7 +3261,7 @@
         <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E35">
         <v>4</v>
@@ -3271,7 +3281,7 @@
         <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -3291,7 +3301,7 @@
         <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3311,7 +3321,7 @@
         <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E38">
         <v>4</v>
@@ -3331,7 +3341,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -3351,7 +3361,7 @@
         <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E40">
         <v>4</v>
@@ -3371,7 +3381,7 @@
         <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -3391,7 +3401,7 @@
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -3411,7 +3421,7 @@
         <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -3431,7 +3441,7 @@
         <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E44">
         <v>4</v>
@@ -3451,7 +3461,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -3471,7 +3481,7 @@
         <v>98</v>
       </c>
       <c r="D46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3491,7 +3501,7 @@
         <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -3511,7 +3521,7 @@
         <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -3531,7 +3541,7 @@
         <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -3551,7 +3561,7 @@
         <v>102</v>
       </c>
       <c r="D50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E50">
         <v>4</v>
@@ -3571,7 +3581,7 @@
         <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E51">
         <v>2</v>
@@ -3591,7 +3601,7 @@
         <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -3611,7 +3621,7 @@
         <v>106</v>
       </c>
       <c r="D53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -3631,7 +3641,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -3651,7 +3661,7 @@
         <v>108</v>
       </c>
       <c r="D55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -3671,7 +3681,7 @@
         <v>109</v>
       </c>
       <c r="D56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -3691,7 +3701,7 @@
         <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E57">
         <v>2</v>
@@ -3711,7 +3721,7 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E58">
         <v>4</v>
@@ -3731,7 +3741,7 @@
         <v>113</v>
       </c>
       <c r="D59" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -3751,7 +3761,7 @@
         <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -3771,7 +3781,7 @@
         <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -3791,7 +3801,7 @@
         <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -3805,13 +3815,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B63" t="s">
         <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -3825,13 +3835,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B64" t="s">
         <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -3845,13 +3855,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>181</v>
+      </c>
+      <c r="B65" t="s">
         <v>182</v>
       </c>
-      <c r="B65" t="s">
-        <v>183</v>
-      </c>
       <c r="D65" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -4983,7 +4993,7 @@
         <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
         <v>169</v>
@@ -5003,7 +5013,7 @@
         <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
         <v>169</v>
@@ -5026,7 +5036,7 @@
         <v>171</v>
       </c>
       <c r="E12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F12" t="s">
         <v>170</v>
@@ -5040,7 +5050,7 @@
         <v>171</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F13" t="s">
         <v>170</v>
@@ -5463,7 +5473,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
@@ -5483,7 +5493,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -5503,7 +5513,7 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
@@ -5603,19 +5613,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" t="s">
         <v>173</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" t="s">
         <v>174</v>
       </c>
-      <c r="D10" t="s">
-        <v>178</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>175</v>
-      </c>
-      <c r="F10" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5623,19 +5633,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" t="s">
         <v>173</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" t="s">
         <v>174</v>
       </c>
-      <c r="D11" t="s">
-        <v>178</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>175</v>
-      </c>
-      <c r="F11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5643,19 +5653,19 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" t="s">
         <v>173</v>
       </c>
-      <c r="C12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D12" t="s">
-        <v>178</v>
-      </c>
-      <c r="E12" t="s">
-        <v>174</v>
-      </c>
       <c r="F12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5663,13 +5673,13 @@
         <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5677,10 +5687,10 @@
         <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5705,7 +5715,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B3:B5 B10:B11" xr:uid="{9C087D3E-C77C-4FA1-B64D-C267CDBE5ED7}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="B10:B11 B3:B5" xr:uid="{9C087D3E-C77C-4FA1-B64D-C267CDBE5ED7}"/>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8524DA78-77BE-4BD7-B24D-EFEC868B0722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5DA80F-569A-47EF-8054-4299E6E2F1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="656" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="192">
   <si>
     <t>CODIGO</t>
   </si>
@@ -614,10 +614,13 @@
     <t>BIOPROCESSOS (19)</t>
   </si>
   <si>
-    <t>ACE V (35)</t>
-  </si>
-  <si>
     <t> ELABORAÇÃO E ANÁLISE DE PROJETOS (21)</t>
+  </si>
+  <si>
+    <t>ACE 5 (35)</t>
+  </si>
+  <si>
+    <t>TÓPICOS ESPECIAIS EM EFICIÊNCIA ENERGÉTICA EM EDIFÍCIOS (16)</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1550,7 @@
         <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
         <v>186</v>
@@ -1564,7 +1567,7 @@
         <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
         <v>186</v>
@@ -2308,7 +2311,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -2328,7 +2331,7 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
@@ -2348,7 +2351,7 @@
         <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
         <v>121</v>
@@ -2468,7 +2471,7 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
         <v>121</v>
@@ -2488,7 +2491,7 @@
         <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C13" t="s">
         <v>121</v>
@@ -2508,7 +2511,7 @@
         <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C14" t="s">
         <v>121</v>
@@ -2546,7 +2549,7 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F11 A15:F15 A12:A14 C12:F14" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F3 A15:F15 A12:A14 C12:F14 A7:F11 A4 C4:F4 A5:A6 C5:F6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\igorc\Documents\GitProjetos\OFERTA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5DA80F-569A-47EF-8054-4299E6E2F1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB90AAC-BD48-4AB3-BEF7-83DA541CEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="656" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -548,21 +548,12 @@
     <t>FÍSICA 2 (26)</t>
   </si>
   <si>
-    <t>CÁLCULO IV (25)</t>
-  </si>
-  <si>
     <t>ENERGIA DE BIOMASSA E CAPTAÇÃO DE CARBONO (23)</t>
   </si>
   <si>
-    <t>ACE I (1)</t>
-  </si>
-  <si>
     <t>BIOQUÍMICA (4)</t>
   </si>
   <si>
-    <t>FÍSICA III (8)</t>
-  </si>
-  <si>
     <t>TRANSFERÊNCIA DE CALOR (7)</t>
   </si>
   <si>
@@ -621,6 +612,15 @@
   </si>
   <si>
     <t>TÓPICOS ESPECIAIS EM EFICIÊNCIA ENERGÉTICA EM EDIFÍCIOS (16)</t>
+  </si>
+  <si>
+    <t>CÁLCULO 4 (25)</t>
+  </si>
+  <si>
+    <t>ACE 1 (1)</t>
+  </si>
+  <si>
+    <t>FÍSICA 3 (8)</t>
   </si>
 </sst>
 </file>
@@ -1507,19 +1507,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E10" t="s">
         <v>184</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>185</v>
-      </c>
-      <c r="D10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1527,19 +1527,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" t="s">
         <v>184</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>185</v>
-      </c>
-      <c r="D11" t="s">
-        <v>186</v>
-      </c>
-      <c r="E11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1547,16 +1547,16 @@
         <v>136</v>
       </c>
       <c r="C12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" t="s">
         <v>185</v>
-      </c>
-      <c r="D12" t="s">
-        <v>190</v>
-      </c>
-      <c r="E12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F12" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,13 +1564,13 @@
         <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1578,7 +1578,7 @@
         <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2311,7 +2311,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -2331,7 +2331,7 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
@@ -2351,7 +2351,7 @@
         <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
         <v>121</v>
@@ -2471,7 +2471,7 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
         <v>121</v>
@@ -2491,7 +2491,7 @@
         <v>137</v>
       </c>
       <c r="B13" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
         <v>121</v>
@@ -2511,7 +2511,7 @@
         <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C14" t="s">
         <v>121</v>
@@ -2578,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E1" t="s">
         <v>41</v>
@@ -2604,7 +2604,7 @@
         <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -2624,7 +2624,7 @@
         <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2644,7 +2644,7 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2684,7 +2684,7 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -2704,7 +2704,7 @@
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -2724,7 +2724,7 @@
         <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -2744,7 +2744,7 @@
         <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -2764,7 +2764,7 @@
         <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -2784,7 +2784,7 @@
         <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -2804,7 +2804,7 @@
         <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -2824,7 +2824,7 @@
         <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -2844,7 +2844,7 @@
         <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -2864,7 +2864,7 @@
         <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -2884,7 +2884,7 @@
         <v>64</v>
       </c>
       <c r="D16" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -2904,7 +2904,7 @@
         <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E17">
         <v>4</v>
@@ -2924,7 +2924,7 @@
         <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -2944,7 +2944,7 @@
         <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2964,7 +2964,7 @@
         <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2984,7 +2984,7 @@
         <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -3004,7 +3004,7 @@
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -3024,7 +3024,7 @@
         <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -3044,7 +3044,7 @@
         <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -3064,7 +3064,7 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -3084,7 +3084,7 @@
         <v>75</v>
       </c>
       <c r="D26" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -3104,7 +3104,7 @@
         <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -3124,7 +3124,7 @@
         <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -3144,7 +3144,7 @@
         <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -3164,7 +3164,7 @@
         <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E30">
         <v>4</v>
@@ -3184,7 +3184,7 @@
         <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -3204,7 +3204,7 @@
         <v>82</v>
       </c>
       <c r="D32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E32">
         <v>3</v>
@@ -3224,7 +3224,7 @@
         <v>83</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -3244,7 +3244,7 @@
         <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -3264,7 +3264,7 @@
         <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E35">
         <v>4</v>
@@ -3284,7 +3284,7 @@
         <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -3304,7 +3304,7 @@
         <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E37">
         <v>3</v>
@@ -3324,7 +3324,7 @@
         <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E38">
         <v>4</v>
@@ -3344,7 +3344,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -3364,7 +3364,7 @@
         <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E40">
         <v>4</v>
@@ -3384,7 +3384,7 @@
         <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -3404,7 +3404,7 @@
         <v>93</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -3424,7 +3424,7 @@
         <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -3444,7 +3444,7 @@
         <v>96</v>
       </c>
       <c r="D44" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E44">
         <v>4</v>
@@ -3464,7 +3464,7 @@
         <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -3484,7 +3484,7 @@
         <v>98</v>
       </c>
       <c r="D46" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -3504,7 +3504,7 @@
         <v>99</v>
       </c>
       <c r="D47" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -3524,7 +3524,7 @@
         <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E48">
         <v>3</v>
@@ -3544,7 +3544,7 @@
         <v>101</v>
       </c>
       <c r="D49" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -3564,7 +3564,7 @@
         <v>102</v>
       </c>
       <c r="D50" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E50">
         <v>4</v>
@@ -3584,7 +3584,7 @@
         <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E51">
         <v>2</v>
@@ -3604,7 +3604,7 @@
         <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -3624,7 +3624,7 @@
         <v>106</v>
       </c>
       <c r="D53" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E53">
         <v>4</v>
@@ -3644,7 +3644,7 @@
         <v>107</v>
       </c>
       <c r="D54" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E54">
         <v>3</v>
@@ -3664,7 +3664,7 @@
         <v>108</v>
       </c>
       <c r="D55" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E55">
         <v>3</v>
@@ -3684,7 +3684,7 @@
         <v>109</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -3704,7 +3704,7 @@
         <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E57">
         <v>2</v>
@@ -3724,7 +3724,7 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E58">
         <v>4</v>
@@ -3744,7 +3744,7 @@
         <v>113</v>
       </c>
       <c r="D59" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E59">
         <v>3</v>
@@ -3764,7 +3764,7 @@
         <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -3784,7 +3784,7 @@
         <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E61">
         <v>3</v>
@@ -3804,7 +3804,7 @@
         <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -3818,13 +3818,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B63" t="s">
         <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E63">
         <v>3</v>
@@ -3838,13 +3838,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B64" t="s">
         <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -3858,13 +3858,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D65" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -4951,10 +4951,10 @@
         <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4962,10 +4962,10 @@
         <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="D8" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,19 +4993,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" t="s">
         <v>168</v>
       </c>
-      <c r="C10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" t="s">
-        <v>170</v>
-      </c>
       <c r="F10" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5013,19 +5013,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E11" t="s">
         <v>168</v>
       </c>
-      <c r="C11" t="s">
-        <v>178</v>
-      </c>
-      <c r="D11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" t="s">
-        <v>170</v>
-      </c>
       <c r="F11" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5033,16 +5033,16 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E12" t="s">
+        <v>175</v>
+      </c>
+      <c r="F12" t="s">
         <v>168</v>
-      </c>
-      <c r="D12" t="s">
-        <v>171</v>
-      </c>
-      <c r="E12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F12" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5050,13 +5050,13 @@
         <v>137</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5476,7 +5476,7 @@
         <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
         <v>121</v>
@@ -5496,7 +5496,7 @@
         <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -5516,7 +5516,7 @@
         <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
         <v>121</v>
@@ -5616,19 +5616,19 @@
         <v>133</v>
       </c>
       <c r="B10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" t="s">
         <v>172</v>
-      </c>
-      <c r="C10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F10" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5636,19 +5636,19 @@
         <v>135</v>
       </c>
       <c r="B11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" t="s">
         <v>172</v>
-      </c>
-      <c r="C11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" t="s">
-        <v>177</v>
-      </c>
-      <c r="E11" t="s">
-        <v>174</v>
-      </c>
-      <c r="F11" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5656,19 +5656,19 @@
         <v>136</v>
       </c>
       <c r="B12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E12" t="s">
+        <v>170</v>
+      </c>
+      <c r="F12" t="s">
         <v>172</v>
-      </c>
-      <c r="C12" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5676,13 +5676,13 @@
         <v>137</v>
       </c>
       <c r="C13" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5690,10 +5690,10 @@
         <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB90AAC-BD48-4AB3-BEF7-83DA541CEDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="656" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="656" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PROFESSORES" sheetId="1" r:id="rId1"/>
